--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,57 +934,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136795179</v>
+        <v>136821353</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>92325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>3008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375408</v>
+        <v>375769</v>
       </c>
       <c r="R4" t="n">
-        <v>6669888</v>
+        <v>6670128</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,51 +1040,60 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795179</t>
+          <t>https://artportalen.se/Sighting/136821353</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136795165</v>
+        <v>136795179</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375207</v>
+        <v>375408</v>
       </c>
       <c r="R5" t="n">
-        <v>6670161</v>
+        <v>6669888</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,21 +1146,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1181,16 +1161,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795165</t>
+          <t>https://artportalen.se/Sighting/136795179</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136795167</v>
+        <v>136821355</v>
       </c>
       <c r="B6" t="n">
-        <v>79233</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,37 +1178,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375137</v>
+        <v>375905</v>
       </c>
       <c r="R6" t="n">
-        <v>6670153</v>
+        <v>6670094</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,22 +1241,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,16 +1282,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795167</t>
+          <t>https://artportalen.se/Sighting/136821355</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136795174</v>
+        <v>136821362</v>
       </c>
       <c r="B7" t="n">
-        <v>79233</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,34 +1299,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375372</v>
+        <v>375746</v>
       </c>
       <c r="R7" t="n">
-        <v>6669927</v>
+        <v>6670034</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1364,22 +1362,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,38 +1403,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795174</t>
+          <t>https://artportalen.se/Sighting/136821362</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136795175</v>
+        <v>136795165</v>
       </c>
       <c r="B8" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1446,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375465</v>
+        <v>375207</v>
       </c>
       <c r="R8" t="n">
-        <v>6669999</v>
+        <v>6670161</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1489,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,6 +1505,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1517,38 +1535,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795175</t>
+          <t>https://artportalen.se/Sighting/136795165</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136795181</v>
+        <v>136821366</v>
       </c>
       <c r="B9" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,13 +1576,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375504</v>
+        <v>375576</v>
       </c>
       <c r="R9" t="n">
-        <v>6670028</v>
+        <v>6669863</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,22 +1606,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,38 +1647,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795181</t>
+          <t>https://artportalen.se/Sighting/136821366</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136795184</v>
+        <v>136821369</v>
       </c>
       <c r="B10" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1670,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375507</v>
+        <v>375444</v>
       </c>
       <c r="R10" t="n">
-        <v>6670034</v>
+        <v>6669803</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1700,22 +1718,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,56 +1759,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795184</t>
+          <t>https://artportalen.se/Sighting/136821369</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136795190</v>
+        <v>136795167</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375547</v>
+        <v>375137</v>
       </c>
       <c r="R11" t="n">
-        <v>6669921</v>
+        <v>6670153</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1822,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1845,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,59 +1871,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795190</t>
+          <t>https://artportalen.se/Sighting/136795167</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136795169</v>
+        <v>136795174</v>
       </c>
       <c r="B12" t="n">
-        <v>8463</v>
+        <v>79233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375318</v>
+        <v>375372</v>
       </c>
       <c r="R12" t="n">
-        <v>6670152</v>
+        <v>6669927</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1949,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,21 +1968,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1990,59 +1983,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795169</t>
+          <t>https://artportalen.se/Sighting/136795174</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136795186</v>
+        <v>136795175</v>
       </c>
       <c r="B13" t="n">
-        <v>8463</v>
+        <v>79233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375569</v>
+        <v>375465</v>
       </c>
       <c r="R13" t="n">
-        <v>6670040</v>
+        <v>6669999</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2071,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,21 +2080,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2122,58 +2095,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795186</t>
+          <t>https://artportalen.se/Sighting/136795175</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136795185</v>
+        <v>136795181</v>
       </c>
       <c r="B14" t="n">
-        <v>99268</v>
+        <v>79233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375520</v>
+        <v>375504</v>
       </c>
       <c r="R14" t="n">
-        <v>6670059</v>
+        <v>6670028</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2202,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2212,7 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,38 +2207,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795185</t>
+          <t>https://artportalen.se/Sighting/136795181</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136795170</v>
+        <v>136795184</v>
       </c>
       <c r="B15" t="n">
-        <v>98213</v>
+        <v>79233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375450</v>
+        <v>375507</v>
       </c>
       <c r="R15" t="n">
-        <v>6670180</v>
+        <v>6670034</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2314,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2324,7 +2293,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,16 +2319,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795170</t>
+          <t>https://artportalen.se/Sighting/136795184</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136795173</v>
+        <v>136821365</v>
       </c>
       <c r="B16" t="n">
-        <v>79234</v>
+        <v>79233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,21 +2336,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2391,13 +2360,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375476</v>
+        <v>375581</v>
       </c>
       <c r="R16" t="n">
-        <v>6670112</v>
+        <v>6669867</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2421,22 +2390,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,16 +2431,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795173</t>
+          <t>https://artportalen.se/Sighting/136821365</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136795176</v>
+        <v>136821367</v>
       </c>
       <c r="B17" t="n">
-        <v>79234</v>
+        <v>79233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,21 +2448,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2503,13 +2472,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375465</v>
+        <v>375565</v>
       </c>
       <c r="R17" t="n">
-        <v>6669999</v>
+        <v>6669859</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2533,22 +2502,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,51 +2543,56 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795176</t>
+          <t>https://artportalen.se/Sighting/136821367</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136795180</v>
+        <v>136795190</v>
       </c>
       <c r="B18" t="n">
-        <v>79234</v>
+        <v>58005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375480</v>
+        <v>375547</v>
       </c>
       <c r="R18" t="n">
-        <v>6670027</v>
+        <v>6669921</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2650,7 +2624,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2660,7 +2634,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,51 +2660,60 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795180</t>
+          <t>https://artportalen.se/Sighting/136795190</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136795188</v>
+        <v>136821364</v>
       </c>
       <c r="B19" t="n">
-        <v>79234</v>
+        <v>57195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375567</v>
+        <v>375694</v>
       </c>
       <c r="R19" t="n">
-        <v>6670017</v>
+        <v>6669902</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2757,22 +2740,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tupp stöttes</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,54 +2786,59 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795188</t>
+          <t>https://artportalen.se/Sighting/136821364</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136795191</v>
+        <v>136821347</v>
       </c>
       <c r="B20" t="n">
-        <v>79234</v>
+        <v>57198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375545</v>
+        <v>375327</v>
       </c>
       <c r="R20" t="n">
-        <v>6669917</v>
+        <v>6669913</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2869,22 +2862,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2909,6 +2902,1780 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821347</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136821357</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>375890</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6670039</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821357</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136821370</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>375441</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6669799</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821370</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136795169</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>375318</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6670152</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795169</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136795186</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>375569</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6670040</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795186</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136821351</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>375654</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6670285</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821351</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136795185</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>375520</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6670059</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795185</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136821356</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>375908</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6670081</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821356</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136821360</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>375747</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6669937</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821360</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136821361</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>375768</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6669986</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821361</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136795170</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>375450</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6670180</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795170</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136795173</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>375476</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6670112</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795173</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136795176</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>375465</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6669999</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795176</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136795180</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>375480</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6670027</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795180</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136795188</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>375567</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6670017</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795188</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136795191</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>375545</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6669917</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136795191</t>
         </is>
@@ -2935,6 +4702,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136795189</v>
+        <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>97681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375599</v>
+        <v>375767</v>
       </c>
       <c r="R2" t="n">
-        <v>6669959</v>
+        <v>6670091</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,70 +773,81 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris # Låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795189</t>
+          <t>https://artportalen.se/Sighting/136830764</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136795168</v>
+        <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92325</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3008</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375272</v>
+        <v>375599</v>
       </c>
       <c r="R3" t="n">
-        <v>6670193</v>
+        <v>6669959</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,17 +916,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,13 +943,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795168</t>
+          <t>https://artportalen.se/Sighting/136795189</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136821353</v>
+        <v>136795168</v>
       </c>
       <c r="B4" t="n">
         <v>92325</v>
@@ -969,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375769</v>
+        <v>375272</v>
       </c>
       <c r="R4" t="n">
-        <v>6670128</v>
+        <v>6670193</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +1014,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,6 +1040,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1040,63 +1070,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821353</t>
+          <t>https://artportalen.se/Sighting/136795168</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136795179</v>
+        <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>92325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>3008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375408</v>
+        <v>375769</v>
       </c>
       <c r="R5" t="n">
-        <v>6669888</v>
+        <v>6670128</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1141,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,63 +1182,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795179</t>
+          <t>https://artportalen.se/Sighting/136821353</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136821355</v>
+        <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>92327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>3008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375905</v>
+        <v>375794</v>
       </c>
       <c r="R6" t="n">
-        <v>6670094</v>
+        <v>6670087</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1268,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,61 +1283,52 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821355</t>
+          <t>https://artportalen.se/Sighting/136830765</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136821362</v>
+        <v>136830762</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>91889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -1335,7 +1338,7 @@
         <v>375746</v>
       </c>
       <c r="R7" t="n">
-        <v>6670034</v>
+        <v>6670107</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1367,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,49 +1395,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821362</t>
+          <t>https://artportalen.se/Sighting/136830762</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136795165</v>
+        <v>136830780</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>91889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1444,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375207</v>
+        <v>375716</v>
       </c>
       <c r="R8" t="n">
-        <v>6670161</v>
+        <v>6670067</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,27 +1477,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Riklig på tall</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,84 +1503,78 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795165</t>
+          <t>https://artportalen.se/Sighting/136830780</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136821366</v>
+        <v>136795179</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375576</v>
+        <v>375408</v>
       </c>
       <c r="R9" t="n">
-        <v>6669863</v>
+        <v>6669888</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,22 +1598,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,54 +1639,63 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821366</t>
+          <t>https://artportalen.se/Sighting/136795179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136821369</v>
+        <v>136821355</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375444</v>
+        <v>375905</v>
       </c>
       <c r="R10" t="n">
-        <v>6669803</v>
+        <v>6670094</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1724,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1734,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,16 +1760,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821369</t>
+          <t>https://artportalen.se/Sighting/136821355</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136795167</v>
+        <v>136821362</v>
       </c>
       <c r="B11" t="n">
-        <v>79233</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,37 +1777,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375137</v>
+        <v>375746</v>
       </c>
       <c r="R11" t="n">
-        <v>6670153</v>
+        <v>6670034</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1830,22 +1840,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,16 +1881,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795167</t>
+          <t>https://artportalen.se/Sighting/136821362</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136795174</v>
+        <v>136847994</v>
       </c>
       <c r="B12" t="n">
-        <v>79233</v>
+        <v>93447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,37 +1898,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375372</v>
+        <v>375776</v>
       </c>
       <c r="R12" t="n">
-        <v>6669927</v>
+        <v>6670053</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,22 +1955,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Några stycken.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,55 +1974,61 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Fuktig grandominerad sänka i en annars talldominerad skog.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795174</t>
+          <t>https://artportalen.se/Sighting/136847994</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136795175</v>
+        <v>136795165</v>
       </c>
       <c r="B13" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +2038,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375465</v>
+        <v>375207</v>
       </c>
       <c r="R13" t="n">
-        <v>6669999</v>
+        <v>6670161</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2059,7 +2073,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2083,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Riklig på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,6 +2099,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2095,38 +2129,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795175</t>
+          <t>https://artportalen.se/Sighting/136795165</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136795181</v>
+        <v>136821366</v>
       </c>
       <c r="B14" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2136,13 +2170,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375504</v>
+        <v>375576</v>
       </c>
       <c r="R14" t="n">
-        <v>6670028</v>
+        <v>6669863</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,22 +2200,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,38 +2241,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795181</t>
+          <t>https://artportalen.se/Sighting/136821366</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136795184</v>
+        <v>136821369</v>
       </c>
       <c r="B15" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2248,10 +2282,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375507</v>
+        <v>375444</v>
       </c>
       <c r="R15" t="n">
-        <v>6670034</v>
+        <v>6669803</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2278,22 +2312,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,38 +2353,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795184</t>
+          <t>https://artportalen.se/Sighting/136821369</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136821365</v>
+        <v>136830752</v>
       </c>
       <c r="B16" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2360,13 +2394,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375581</v>
+        <v>375546</v>
       </c>
       <c r="R16" t="n">
-        <v>6669867</v>
+        <v>6670241</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2395,7 +2429,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2439,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,49 +2454,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821365</t>
+          <t>https://artportalen.se/Sighting/136830752</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136821367</v>
+        <v>136830767</v>
       </c>
       <c r="B17" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2472,13 +2506,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375565</v>
+        <v>375906</v>
       </c>
       <c r="R17" t="n">
-        <v>6669859</v>
+        <v>6670099</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,7 +2541,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2551,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,67 +2566,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821367</t>
+          <t>https://artportalen.se/Sighting/136830767</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136795190</v>
+        <v>136795167</v>
       </c>
       <c r="B18" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375547</v>
+        <v>375137</v>
       </c>
       <c r="R18" t="n">
-        <v>6669921</v>
+        <v>6670153</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2624,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,63 +2689,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795190</t>
+          <t>https://artportalen.se/Sighting/136795167</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136821364</v>
+        <v>136795174</v>
       </c>
       <c r="B19" t="n">
-        <v>57195</v>
+        <v>79233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375694</v>
+        <v>375372</v>
       </c>
       <c r="R19" t="n">
-        <v>6669902</v>
+        <v>6669927</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2740,27 +2760,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tupp stöttes</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,56 +2801,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821364</t>
+          <t>https://artportalen.se/Sighting/136795174</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136821347</v>
+        <v>136795175</v>
       </c>
       <c r="B20" t="n">
-        <v>57198</v>
+        <v>79233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375327</v>
+        <v>375465</v>
       </c>
       <c r="R20" t="n">
-        <v>6669913</v>
+        <v>6669999</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2862,22 +2872,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,16 +2913,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821347</t>
+          <t>https://artportalen.se/Sighting/136795175</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136821357</v>
+        <v>136795181</v>
       </c>
       <c r="B21" t="n">
-        <v>58169</v>
+        <v>79233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,46 +2930,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375890</v>
+        <v>375504</v>
       </c>
       <c r="R21" t="n">
-        <v>6670039</v>
+        <v>6670028</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2983,22 +2984,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3024,60 +3025,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821357</t>
+          <t>https://artportalen.se/Sighting/136795181</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136821370</v>
+        <v>136795184</v>
       </c>
       <c r="B22" t="n">
-        <v>58629</v>
+        <v>79233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103041</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375441</v>
+        <v>375507</v>
       </c>
       <c r="R22" t="n">
-        <v>6669799</v>
+        <v>6670034</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3104,22 +3096,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3145,59 +3137,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821370</t>
+          <t>https://artportalen.se/Sighting/136795184</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136795169</v>
+        <v>136821365</v>
       </c>
       <c r="B23" t="n">
-        <v>8463</v>
+        <v>79233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375318</v>
+        <v>375581</v>
       </c>
       <c r="R23" t="n">
-        <v>6670152</v>
+        <v>6669867</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3221,22 +3208,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,21 +3234,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3277,59 +3249,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795169</t>
+          <t>https://artportalen.se/Sighting/136821365</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136795186</v>
+        <v>136821367</v>
       </c>
       <c r="B24" t="n">
-        <v>8463</v>
+        <v>79233</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375569</v>
+        <v>375565</v>
       </c>
       <c r="R24" t="n">
-        <v>6670040</v>
+        <v>6669859</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3353,22 +3320,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3379,21 +3346,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3409,59 +3361,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795186</t>
+          <t>https://artportalen.se/Sighting/136821367</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136821351</v>
+        <v>136830783</v>
       </c>
       <c r="B25" t="n">
-        <v>8463</v>
+        <v>79233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375654</v>
+        <v>375726</v>
       </c>
       <c r="R25" t="n">
-        <v>6670285</v>
+        <v>6670027</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3490,7 +3437,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3447,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,69 +3462,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821351</t>
+          <t>https://artportalen.se/Sighting/136830783</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136795185</v>
+        <v>136830785</v>
       </c>
       <c r="B26" t="n">
-        <v>99268</v>
+        <v>79233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375520</v>
+        <v>375623</v>
       </c>
       <c r="R26" t="n">
-        <v>6670059</v>
+        <v>6670015</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3601,22 +3544,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,27 +3574,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795185</t>
+          <t>https://artportalen.se/Sighting/136830785</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136821356</v>
+        <v>136795190</v>
       </c>
       <c r="B27" t="n">
-        <v>99268</v>
+        <v>58005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3659,31 +3602,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3692,10 +3631,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375908</v>
+        <v>375547</v>
       </c>
       <c r="R27" t="n">
-        <v>6670081</v>
+        <v>6669921</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3722,22 +3661,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,16 +3702,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821356</t>
+          <t>https://artportalen.se/Sighting/136795190</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136821360</v>
+        <v>136830758</v>
       </c>
       <c r="B28" t="n">
-        <v>99268</v>
+        <v>58005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3780,46 +3719,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375747</v>
+        <v>375693</v>
       </c>
       <c r="R28" t="n">
-        <v>6669937</v>
+        <v>6670228</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3848,7 +3778,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3858,7 +3788,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,27 +3808,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821360</t>
+          <t>https://artportalen.se/Sighting/136830758</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136821361</v>
+        <v>136830775</v>
       </c>
       <c r="B29" t="n">
-        <v>99268</v>
+        <v>58005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,43 +3836,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375768</v>
+        <v>375853</v>
       </c>
       <c r="R29" t="n">
-        <v>6669986</v>
+        <v>6670087</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3969,7 +3895,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3979,7 +3905,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3994,27 +3925,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821361</t>
+          <t>https://artportalen.se/Sighting/136830775</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136795170</v>
+        <v>136830787</v>
       </c>
       <c r="B30" t="n">
-        <v>98213</v>
+        <v>58005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4022,21 +3953,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4046,10 +3977,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375450</v>
+        <v>375562</v>
       </c>
       <c r="R30" t="n">
-        <v>6670180</v>
+        <v>6670005</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4076,22 +4007,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4106,49 +4042,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795170</t>
+          <t>https://artportalen.se/Sighting/136830787</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136795173</v>
+        <v>136830789</v>
       </c>
       <c r="B31" t="n">
-        <v>79234</v>
+        <v>58005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4158,10 +4094,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375476</v>
+        <v>375449</v>
       </c>
       <c r="R31" t="n">
-        <v>6670112</v>
+        <v>6669946</v>
       </c>
       <c r="S31" t="n">
         <v>6</v>
@@ -4188,22 +4124,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4218,62 +4159,71 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795173</t>
+          <t>https://artportalen.se/Sighting/136830789</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136795176</v>
+        <v>136821364</v>
       </c>
       <c r="B32" t="n">
-        <v>79234</v>
+        <v>57195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375465</v>
+        <v>375694</v>
       </c>
       <c r="R32" t="n">
-        <v>6669999</v>
+        <v>6669902</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4300,22 +4250,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tupp stöttes</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4341,54 +4296,58 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795176</t>
+          <t>https://artportalen.se/Sighting/136821364</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136795180</v>
+        <v>136830766</v>
       </c>
       <c r="B33" t="n">
-        <v>79234</v>
+        <v>57195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>375480</v>
+        <v>375884</v>
       </c>
       <c r="R33" t="n">
-        <v>6670027</v>
+        <v>6670111</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4412,22 +4371,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4442,62 +4406,67 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795180</t>
+          <t>https://artportalen.se/Sighting/136830766</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136795188</v>
+        <v>136821347</v>
       </c>
       <c r="B34" t="n">
-        <v>79234</v>
+        <v>57198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>375567</v>
+        <v>375327</v>
       </c>
       <c r="R34" t="n">
-        <v>6670017</v>
+        <v>6669913</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4524,22 +4493,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4565,16 +4534,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795188</t>
+          <t>https://artportalen.se/Sighting/136821347</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136795191</v>
+        <v>136821357</v>
       </c>
       <c r="B35" t="n">
-        <v>79234</v>
+        <v>58169</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4582,37 +4551,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>375545</v>
+        <v>375890</v>
       </c>
       <c r="R35" t="n">
-        <v>6669917</v>
+        <v>6670039</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4636,22 +4614,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4677,7 +4655,3723 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136821357</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136830786</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>375599</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6670026</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830786</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136830748</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>375478</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6670141</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830748</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136830772</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>376001</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6670081</v>
+      </c>
+      <c r="S38" t="n">
+        <v>14</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830772</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136830778</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>375833</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6670068</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830778</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136821370</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>375441</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6669799</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821370</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136830747</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>375482</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6670128</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830747</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136795169</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>375318</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6670152</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795169</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136795186</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>375569</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6670040</v>
+      </c>
+      <c r="S43" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795186</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136821351</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>375654</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6670285</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821351</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136830754</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>375623</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6670238</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830754</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136830755</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>375652</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6670242</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Mer färska spår</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830755</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136830756</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>375661</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6670269</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830756</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136830759</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>375693</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6670228</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830759</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136830760</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>375728</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6670132</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830760</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136830774</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>375850</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6670075</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830774</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136830776</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>375853</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6670087</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830776</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136830790</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>375449</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6669946</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830790</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136830791</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>375461</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6669933</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830791</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136830751</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>375557</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6670167</v>
+      </c>
+      <c r="S54" t="n">
+        <v>9</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830751</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136830761</v>
+      </c>
+      <c r="B55" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>375752</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6670115</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830761</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136795185</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>375520</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6670059</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795185</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136821356</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>375908</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6670081</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821356</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136821360</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>375747</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6669937</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821360</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136821361</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99268</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>375768</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6669986</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821361</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136830781</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>375712</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6670070</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Torra frökapslar</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830781</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136795170</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>375450</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6670180</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795170</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136795173</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>375476</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6670112</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795173</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136795176</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>375465</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6669999</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795176</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136795180</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>375480</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6670027</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795180</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136795188</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>375567</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6670017</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795188</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136795191</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>375545</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6669917</v>
+      </c>
+      <c r="S66" t="n">
+        <v>7</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136795191</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136830784</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>375623</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6670015</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830784</t>
         </is>
       </c>
     </row>
@@ -4717,6 +8411,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136795179</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>136821355</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>136821362</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>136795185</v>
       </c>
       <c r="B56" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>136821356</v>
       </c>
       <c r="B57" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>136821360</v>
       </c>
       <c r="B58" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136821361</v>
       </c>
       <c r="B59" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>136795170</v>
       </c>
       <c r="B61" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136830762</v>
+        <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>91889</v>
+        <v>92327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,37 +1311,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>3008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375746</v>
+        <v>375172</v>
       </c>
       <c r="R7" t="n">
-        <v>6670107</v>
+        <v>6669731</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,22 +1368,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,6 +1382,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,13 +1400,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830762</t>
+          <t>https://artportalen.se/Sighting/136884160</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136830780</v>
+        <v>136830762</v>
       </c>
       <c r="B8" t="n">
         <v>91889</v>
@@ -1447,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375716</v>
+        <v>375746</v>
       </c>
       <c r="R8" t="n">
-        <v>6670067</v>
+        <v>6670107</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,60 +1512,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830780</t>
+          <t>https://artportalen.se/Sighting/136830762</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136795179</v>
+        <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>91889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375408</v>
+        <v>375716</v>
       </c>
       <c r="R9" t="n">
-        <v>6669888</v>
+        <v>6670067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1598,22 +1583,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,24 +1613,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795179</t>
+          <t>https://artportalen.se/Sighting/136830780</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136821355</v>
+        <v>136795179</v>
       </c>
       <c r="B10" t="n">
         <v>93411</v>
@@ -1675,7 +1660,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1689,13 +1674,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375905</v>
+        <v>375408</v>
       </c>
       <c r="R10" t="n">
-        <v>6670094</v>
+        <v>6669888</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,22 +1704,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,16 +1745,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821355</t>
+          <t>https://artportalen.se/Sighting/136795179</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136821362</v>
+        <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93447</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,26 +1762,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1810,13 +1795,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375746</v>
+        <v>375905</v>
       </c>
       <c r="R11" t="n">
-        <v>6670034</v>
+        <v>6670094</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1845,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1855,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,13 +1866,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821362</t>
+          <t>https://artportalen.se/Sighting/136821355</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136847994</v>
+        <v>136821362</v>
       </c>
       <c r="B12" t="n">
         <v>93447</v>
@@ -1915,23 +1900,29 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375776</v>
+        <v>375746</v>
       </c>
       <c r="R12" t="n">
-        <v>6670053</v>
+        <v>6670034</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1958,14 +1949,19 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Några stycken.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,77 +1970,74 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Fuktig grandominerad sänka i en annars talldominerad skog.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136847994</t>
+          <t>https://artportalen.se/Sighting/136821362</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136795165</v>
+        <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>93447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375207</v>
+        <v>375776</v>
       </c>
       <c r="R13" t="n">
-        <v>6670161</v>
+        <v>6670053</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,27 +2061,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Riklig på tall</t>
+          <t>Några stycken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,45 +2080,36 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Fuktig grandominerad sänka i en annars talldominerad skog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795165</t>
+          <t>https://artportalen.se/Sighting/136847994</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136821366</v>
+        <v>136795165</v>
       </c>
       <c r="B14" t="n">
         <v>79476</v>
@@ -2170,13 +2144,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375576</v>
+        <v>375207</v>
       </c>
       <c r="R14" t="n">
-        <v>6669863</v>
+        <v>6670161</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2200,22 +2174,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,6 +2205,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2241,13 +2235,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821366</t>
+          <t>https://artportalen.se/Sighting/136795165</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136821369</v>
+        <v>136821366</v>
       </c>
       <c r="B15" t="n">
         <v>79476</v>
@@ -2282,13 +2276,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375444</v>
+        <v>375576</v>
       </c>
       <c r="R15" t="n">
-        <v>6669803</v>
+        <v>6669863</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2317,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2327,7 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,13 +2347,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821369</t>
+          <t>https://artportalen.se/Sighting/136821366</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136830752</v>
+        <v>136821369</v>
       </c>
       <c r="B16" t="n">
         <v>79476</v>
@@ -2394,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375546</v>
+        <v>375444</v>
       </c>
       <c r="R16" t="n">
-        <v>6670241</v>
+        <v>6669803</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2429,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2439,7 +2433,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,24 +2448,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830752</t>
+          <t>https://artportalen.se/Sighting/136821369</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136830767</v>
+        <v>136830752</v>
       </c>
       <c r="B17" t="n">
         <v>79476</v>
@@ -2506,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375906</v>
+        <v>375546</v>
       </c>
       <c r="R17" t="n">
-        <v>6670099</v>
+        <v>6670241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2541,7 +2535,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2551,7 +2545,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,38 +2571,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830767</t>
+          <t>https://artportalen.se/Sighting/136830752</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136795167</v>
+        <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79233</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2618,10 +2612,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375137</v>
+        <v>375906</v>
       </c>
       <c r="R18" t="n">
-        <v>6670153</v>
+        <v>6670099</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2648,22 +2642,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,65 +2672,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795167</t>
+          <t>https://artportalen.se/Sighting/136830767</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136795174</v>
+        <v>136765417</v>
       </c>
       <c r="B19" t="n">
-        <v>79233</v>
+        <v>79500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375372</v>
+        <v>375284</v>
       </c>
       <c r="R19" t="n">
-        <v>6669927</v>
+        <v>6669768</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,22 +2754,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,65 +2784,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795174</t>
+          <t>https://artportalen.se/Sighting/136765417</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136795175</v>
+        <v>136765632</v>
       </c>
       <c r="B20" t="n">
-        <v>79233</v>
+        <v>79500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375465</v>
+        <v>375291</v>
       </c>
       <c r="R20" t="n">
-        <v>6669999</v>
+        <v>6669744</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,22 +2866,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,65 +2896,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795175</t>
+          <t>https://artportalen.se/Sighting/136765632</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136795181</v>
+        <v>136765741</v>
       </c>
       <c r="B21" t="n">
-        <v>79233</v>
+        <v>79500</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375504</v>
+        <v>375262</v>
       </c>
       <c r="R21" t="n">
-        <v>6670028</v>
+        <v>6669762</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2984,22 +2982,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,65 +3012,68 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795181</t>
+          <t>https://artportalen.se/Sighting/136765741</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136795184</v>
+        <v>136884148</v>
       </c>
       <c r="B22" t="n">
-        <v>79233</v>
+        <v>79500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375507</v>
+        <v>375242</v>
       </c>
       <c r="R22" t="n">
-        <v>6670034</v>
+        <v>6669734</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3096,22 +3097,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,30 +3111,31 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795184</t>
+          <t>https://artportalen.se/Sighting/136884148</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136821365</v>
+        <v>136767140</v>
       </c>
       <c r="B23" t="n">
         <v>79233</v>
@@ -3174,17 +3166,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Backarna, Backarna, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375581</v>
+        <v>375184</v>
       </c>
       <c r="R23" t="n">
-        <v>6669867</v>
+        <v>6669750</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3208,22 +3200,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,24 +3230,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821365</t>
+          <t>https://artportalen.se/Sighting/136767140</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136821367</v>
+        <v>136795167</v>
       </c>
       <c r="B24" t="n">
         <v>79233</v>
@@ -3290,13 +3282,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375565</v>
+        <v>375137</v>
       </c>
       <c r="R24" t="n">
-        <v>6669859</v>
+        <v>6670153</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,22 +3312,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3361,13 +3353,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821367</t>
+          <t>https://artportalen.se/Sighting/136795167</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136830783</v>
+        <v>136795174</v>
       </c>
       <c r="B25" t="n">
         <v>79233</v>
@@ -3402,13 +3394,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375726</v>
+        <v>375372</v>
       </c>
       <c r="R25" t="n">
-        <v>6670027</v>
+        <v>6669927</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3432,22 +3424,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,24 +3454,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830783</t>
+          <t>https://artportalen.se/Sighting/136795174</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136830785</v>
+        <v>136795175</v>
       </c>
       <c r="B26" t="n">
         <v>79233</v>
@@ -3514,13 +3506,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375623</v>
+        <v>375465</v>
       </c>
       <c r="R26" t="n">
-        <v>6670015</v>
+        <v>6669999</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3544,22 +3536,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,70 +3566,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830785</t>
+          <t>https://artportalen.se/Sighting/136795175</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136795190</v>
+        <v>136795181</v>
       </c>
       <c r="B27" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375547</v>
+        <v>375504</v>
       </c>
       <c r="R27" t="n">
-        <v>6669921</v>
+        <v>6670028</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3666,7 +3653,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3676,7 +3663,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3702,38 +3689,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795190</t>
+          <t>https://artportalen.se/Sighting/136795181</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136830758</v>
+        <v>136795184</v>
       </c>
       <c r="B28" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3743,13 +3730,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375693</v>
+        <v>375507</v>
       </c>
       <c r="R28" t="n">
-        <v>6670228</v>
+        <v>6670034</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3773,27 +3760,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,49 +3790,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830758</t>
+          <t>https://artportalen.se/Sighting/136795184</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136830775</v>
+        <v>136821365</v>
       </c>
       <c r="B29" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3860,13 +3842,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375853</v>
+        <v>375581</v>
       </c>
       <c r="R29" t="n">
-        <v>6670087</v>
+        <v>6669867</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3895,7 +3877,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3905,12 +3887,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3925,49 +3902,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830775</t>
+          <t>https://artportalen.se/Sighting/136821365</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136830787</v>
+        <v>136821367</v>
       </c>
       <c r="B30" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3977,13 +3954,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375562</v>
+        <v>375565</v>
       </c>
       <c r="R30" t="n">
-        <v>6670005</v>
+        <v>6669859</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4012,7 +3989,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4022,12 +3999,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4042,49 +4014,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830787</t>
+          <t>https://artportalen.se/Sighting/136821367</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136830789</v>
+        <v>136830783</v>
       </c>
       <c r="B31" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4094,10 +4066,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375449</v>
+        <v>375726</v>
       </c>
       <c r="R31" t="n">
-        <v>6669946</v>
+        <v>6670027</v>
       </c>
       <c r="S31" t="n">
         <v>6</v>
@@ -4129,7 +4101,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4139,12 +4111,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4170,63 +4137,54 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830789</t>
+          <t>https://artportalen.se/Sighting/136830783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136821364</v>
+        <v>136830785</v>
       </c>
       <c r="B32" t="n">
-        <v>57195</v>
+        <v>79233</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375694</v>
+        <v>375623</v>
       </c>
       <c r="R32" t="n">
-        <v>6669902</v>
+        <v>6670015</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4255,7 +4213,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4265,12 +4223,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tupp stöttes</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4285,27 +4238,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821364</t>
+          <t>https://artportalen.se/Sighting/136830785</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136830766</v>
+        <v>136765556</v>
       </c>
       <c r="B33" t="n">
-        <v>57195</v>
+        <v>58005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4313,41 +4266,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>375884</v>
+        <v>375281</v>
       </c>
       <c r="R33" t="n">
-        <v>6670111</v>
+        <v>6669749</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4371,27 +4325,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4417,16 +4366,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830766</t>
+          <t>https://artportalen.se/Sighting/136765556</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136821347</v>
+        <v>136795190</v>
       </c>
       <c r="B34" t="n">
-        <v>57198</v>
+        <v>58005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,16 +4383,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4454,7 +4403,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4463,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>375327</v>
+        <v>375547</v>
       </c>
       <c r="R34" t="n">
-        <v>6669913</v>
+        <v>6669921</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4493,22 +4442,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4534,63 +4483,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821347</t>
+          <t>https://artportalen.se/Sighting/136795190</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136821357</v>
+        <v>136830758</v>
       </c>
       <c r="B35" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>375890</v>
+        <v>375693</v>
       </c>
       <c r="R35" t="n">
-        <v>6670039</v>
+        <v>6670228</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4619,7 +4559,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4629,7 +4569,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4644,66 +4589,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821357</t>
+          <t>https://artportalen.se/Sighting/136830758</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136830786</v>
+        <v>136830775</v>
       </c>
       <c r="B36" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>375599</v>
+        <v>375853</v>
       </c>
       <c r="R36" t="n">
-        <v>6670026</v>
+        <v>6670087</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4735,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4745,7 +4686,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,16 +4717,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830786</t>
+          <t>https://artportalen.se/Sighting/136830775</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136830748</v>
+        <v>136830787</v>
       </c>
       <c r="B37" t="n">
-        <v>58164</v>
+        <v>58005</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4788,16 +4734,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4812,10 +4758,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>375478</v>
+        <v>375562</v>
       </c>
       <c r="R37" t="n">
-        <v>6670141</v>
+        <v>6670005</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4847,7 +4793,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4857,12 +4803,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4888,16 +4834,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830748</t>
+          <t>https://artportalen.se/Sighting/136830787</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136830772</v>
+        <v>136830789</v>
       </c>
       <c r="B38" t="n">
-        <v>58164</v>
+        <v>58005</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4905,16 +4851,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4922,24 +4868,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376001</v>
+        <v>375449</v>
       </c>
       <c r="R38" t="n">
-        <v>6670081</v>
+        <v>6669946</v>
       </c>
       <c r="S38" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4968,7 +4910,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4978,7 +4920,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5004,16 +4951,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830772</t>
+          <t>https://artportalen.se/Sighting/136830789</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136830778</v>
+        <v>136884549</v>
       </c>
       <c r="B39" t="n">
-        <v>58164</v>
+        <v>58005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5021,16 +4968,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5039,19 +4986,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>375833</v>
+        <v>375035</v>
       </c>
       <c r="R39" t="n">
-        <v>6670068</v>
+        <v>6670063</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5075,22 +5030,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5116,16 +5061,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830778</t>
+          <t>https://artportalen.se/Sighting/136884549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136821370</v>
+        <v>136884555</v>
       </c>
       <c r="B40" t="n">
-        <v>58629</v>
+        <v>58005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5133,46 +5078,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103041</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>375441</v>
+        <v>375050</v>
       </c>
       <c r="R40" t="n">
-        <v>6669799</v>
+        <v>6670085</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5196,22 +5140,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5226,27 +5160,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821370</t>
+          <t>https://artportalen.se/Sighting/136884555</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136830747</v>
+        <v>136884705</v>
       </c>
       <c r="B41" t="n">
-        <v>58629</v>
+        <v>58005</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,41 +5188,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103041</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>375482</v>
+        <v>375291</v>
       </c>
       <c r="R41" t="n">
-        <v>6670128</v>
+        <v>6670056</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,22 +5250,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5347,22 +5275,22 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830747</t>
+          <t>https://artportalen.se/Sighting/136884705</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136795169</v>
+        <v>136821364</v>
       </c>
       <c r="B42" t="n">
-        <v>8463</v>
+        <v>57195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5370,27 +5298,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5399,10 +5331,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>375318</v>
+        <v>375694</v>
       </c>
       <c r="R42" t="n">
-        <v>6670152</v>
+        <v>6669902</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5429,22 +5361,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tupp stöttes</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5455,21 +5392,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5485,16 +5407,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795169</t>
+          <t>https://artportalen.se/Sighting/136821364</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136795186</v>
+        <v>136830766</v>
       </c>
       <c r="B43" t="n">
-        <v>8463</v>
+        <v>57195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,42 +5424,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>375569</v>
+        <v>375884</v>
       </c>
       <c r="R43" t="n">
-        <v>6670040</v>
+        <v>6670111</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5561,22 +5482,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5587,46 +5513,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795186</t>
+          <t>https://artportalen.se/Sighting/136830766</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136821351</v>
+        <v>136821347</v>
       </c>
       <c r="B44" t="n">
-        <v>8463</v>
+        <v>57198</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5634,27 +5545,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5663,10 +5574,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>375654</v>
+        <v>375327</v>
       </c>
       <c r="R44" t="n">
-        <v>6670285</v>
+        <v>6669913</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5698,7 +5609,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5708,7 +5619,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5734,51 +5645,60 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821351</t>
+          <t>https://artportalen.se/Sighting/136821347</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136830754</v>
+        <v>136821357</v>
       </c>
       <c r="B45" t="n">
-        <v>8463</v>
+        <v>58169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>375623</v>
+        <v>375890</v>
       </c>
       <c r="R45" t="n">
-        <v>6670238</v>
+        <v>6670039</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5810,7 +5730,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5820,7 +5740,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5835,62 +5755,66 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830754</t>
+          <t>https://artportalen.se/Sighting/136821357</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136830755</v>
+        <v>136830786</v>
       </c>
       <c r="B46" t="n">
-        <v>8463</v>
+        <v>58169</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>375652</v>
+        <v>375599</v>
       </c>
       <c r="R46" t="n">
-        <v>6670242</v>
+        <v>6670026</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5922,7 +5846,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5932,12 +5856,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Mer färska spår</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5963,54 +5882,62 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830755</t>
+          <t>https://artportalen.se/Sighting/136830786</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136830756</v>
+        <v>136884610</v>
       </c>
       <c r="B47" t="n">
-        <v>8463</v>
+        <v>58169</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>375661</v>
+        <v>375138</v>
       </c>
       <c r="R47" t="n">
-        <v>6670269</v>
+        <v>6670040</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6034,22 +5961,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6069,22 +5986,22 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830756</t>
+          <t>https://artportalen.se/Sighting/136884610</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136830759</v>
+        <v>136830748</v>
       </c>
       <c r="B48" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6092,21 +6009,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6116,13 +6033,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>375693</v>
+        <v>375478</v>
       </c>
       <c r="R48" t="n">
-        <v>6670228</v>
+        <v>6670141</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6151,7 +6068,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6161,7 +6078,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6187,16 +6109,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830759</t>
+          <t>https://artportalen.se/Sighting/136830748</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136830760</v>
+        <v>136830772</v>
       </c>
       <c r="B49" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6204,37 +6126,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>375728</v>
+        <v>376001</v>
       </c>
       <c r="R49" t="n">
-        <v>6670132</v>
+        <v>6670081</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6263,7 +6189,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6273,7 +6199,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6299,16 +6225,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830760</t>
+          <t>https://artportalen.se/Sighting/136830772</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136830774</v>
+        <v>136830778</v>
       </c>
       <c r="B50" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6316,21 +6242,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6340,10 +6266,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>375850</v>
+        <v>375833</v>
       </c>
       <c r="R50" t="n">
-        <v>6670075</v>
+        <v>6670068</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6375,7 +6301,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6385,7 +6311,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6411,16 +6337,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830774</t>
+          <t>https://artportalen.se/Sighting/136830778</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136830776</v>
+        <v>136884192</v>
       </c>
       <c r="B51" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6428,37 +6354,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>375853</v>
+        <v>375171</v>
       </c>
       <c r="R51" t="n">
-        <v>6670087</v>
+        <v>6669761</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6482,22 +6416,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6523,16 +6447,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830776</t>
+          <t>https://artportalen.se/Sighting/136884192</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136830790</v>
+        <v>136821370</v>
       </c>
       <c r="B52" t="n">
-        <v>8463</v>
+        <v>58629</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6540,34 +6464,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>375449</v>
+        <v>375441</v>
       </c>
       <c r="R52" t="n">
-        <v>6669946</v>
+        <v>6669799</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6599,7 +6532,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6609,7 +6542,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6624,27 +6557,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830790</t>
+          <t>https://artportalen.se/Sighting/136821370</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136830791</v>
+        <v>136830747</v>
       </c>
       <c r="B53" t="n">
-        <v>8463</v>
+        <v>58629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6652,34 +6585,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>375461</v>
+        <v>375482</v>
       </c>
       <c r="R53" t="n">
-        <v>6669933</v>
+        <v>6670128</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6711,7 +6648,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6721,7 +6658,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6747,62 +6684,59 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830791</t>
+          <t>https://artportalen.se/Sighting/136830747</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136830751</v>
+        <v>136795169</v>
       </c>
       <c r="B54" t="n">
-        <v>56739</v>
+        <v>8463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>206046</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>hårrester</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>375557</v>
+        <v>375318</v>
       </c>
       <c r="R54" t="n">
-        <v>6670167</v>
+        <v>6670152</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6826,22 +6760,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6852,77 +6786,89 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830751</t>
+          <t>https://artportalen.se/Sighting/136795169</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136830761</v>
+        <v>136795186</v>
       </c>
       <c r="B55" t="n">
-        <v>56739</v>
+        <v>8463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>206046</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>375752</v>
+        <v>375569</v>
       </c>
       <c r="R55" t="n">
-        <v>6670115</v>
+        <v>6670040</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6946,22 +6892,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6972,31 +6918,46 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830761</t>
+          <t>https://artportalen.se/Sighting/136795186</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136795185</v>
+        <v>136821351</v>
       </c>
       <c r="B56" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7004,26 +6965,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7032,10 +6994,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>375520</v>
+        <v>375654</v>
       </c>
       <c r="R56" t="n">
-        <v>6670059</v>
+        <v>6670285</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7062,22 +7024,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7103,16 +7065,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795185</t>
+          <t>https://artportalen.se/Sighting/136821351</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136821356</v>
+        <v>136830754</v>
       </c>
       <c r="B57" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7120,43 +7082,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>375908</v>
+        <v>375623</v>
       </c>
       <c r="R57" t="n">
-        <v>6670081</v>
+        <v>6670238</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7188,7 +7141,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7198,7 +7151,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7213,27 +7166,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821356</t>
+          <t>https://artportalen.se/Sighting/136830754</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136821360</v>
+        <v>136830755</v>
       </c>
       <c r="B58" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7241,43 +7194,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>375747</v>
+        <v>375652</v>
       </c>
       <c r="R58" t="n">
-        <v>6669937</v>
+        <v>6670242</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,7 +7253,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7319,7 +7263,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Mer färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7334,27 +7283,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821360</t>
+          <t>https://artportalen.se/Sighting/136830755</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136821361</v>
+        <v>136830756</v>
       </c>
       <c r="B59" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7362,43 +7311,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>375768</v>
+        <v>375661</v>
       </c>
       <c r="R59" t="n">
-        <v>6669986</v>
+        <v>6670269</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7430,7 +7370,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7440,7 +7380,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7455,27 +7395,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821361</t>
+          <t>https://artportalen.se/Sighting/136830756</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136830781</v>
+        <v>136830759</v>
       </c>
       <c r="B60" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7483,41 +7423,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>375712</v>
+        <v>375693</v>
       </c>
       <c r="R60" t="n">
-        <v>6670070</v>
+        <v>6670228</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7546,7 +7482,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7556,12 +7492,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Torra frökapslar</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7587,16 +7518,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830781</t>
+          <t>https://artportalen.se/Sighting/136830759</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136795170</v>
+        <v>136830760</v>
       </c>
       <c r="B61" t="n">
-        <v>98215</v>
+        <v>8463</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7604,21 +7535,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7628,10 +7559,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>375450</v>
+        <v>375728</v>
       </c>
       <c r="R61" t="n">
-        <v>6670180</v>
+        <v>6670132</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7658,22 +7589,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7688,49 +7619,49 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795170</t>
+          <t>https://artportalen.se/Sighting/136830760</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136795173</v>
+        <v>136830774</v>
       </c>
       <c r="B62" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7740,13 +7671,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>375476</v>
+        <v>375850</v>
       </c>
       <c r="R62" t="n">
-        <v>6670112</v>
+        <v>6670075</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7770,22 +7701,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7800,49 +7731,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795173</t>
+          <t>https://artportalen.se/Sighting/136830774</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136795176</v>
+        <v>136830776</v>
       </c>
       <c r="B63" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7852,10 +7783,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>375465</v>
+        <v>375853</v>
       </c>
       <c r="R63" t="n">
-        <v>6669999</v>
+        <v>6670087</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7882,22 +7813,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7912,49 +7843,49 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795176</t>
+          <t>https://artportalen.se/Sighting/136830776</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136795180</v>
+        <v>136830790</v>
       </c>
       <c r="B64" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7964,10 +7895,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>375480</v>
+        <v>375449</v>
       </c>
       <c r="R64" t="n">
-        <v>6670027</v>
+        <v>6669946</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7994,22 +7925,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8024,49 +7955,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795180</t>
+          <t>https://artportalen.se/Sighting/136830790</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136795188</v>
+        <v>136830791</v>
       </c>
       <c r="B65" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8076,10 +8007,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>375567</v>
+        <v>375461</v>
       </c>
       <c r="R65" t="n">
-        <v>6670017</v>
+        <v>6669933</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8106,22 +8037,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8136,65 +8067,70 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795188</t>
+          <t>https://artportalen.se/Sighting/136830791</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136795191</v>
+        <v>136884662</v>
       </c>
       <c r="B66" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>375545</v>
+        <v>375226</v>
       </c>
       <c r="R66" t="n">
-        <v>6669917</v>
+        <v>6670098</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8218,22 +8154,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8242,71 +8168,77 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795191</t>
+          <t>https://artportalen.se/Sighting/136884662</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136830784</v>
+        <v>136884706</v>
       </c>
       <c r="B67" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>375623</v>
+        <v>375291</v>
       </c>
       <c r="R67" t="n">
-        <v>6670015</v>
+        <v>6670056</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8330,22 +8262,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8354,6 +8276,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8365,13 +8288,1743 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136884706</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136830751</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>375557</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6670167</v>
+      </c>
+      <c r="S68" t="n">
+        <v>9</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830751</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136830761</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>375752</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6670115</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830761</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136795185</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>375520</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6670059</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795185</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136821356</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>375908</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6670081</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821356</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136821360</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>375747</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6669937</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821360</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136821361</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>375768</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6669986</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821361</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136830781</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>375712</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6670070</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Torra frökapslar</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830781</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136795170</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>375450</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6670180</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795170</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136795173</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>375476</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6670112</v>
+      </c>
+      <c r="S76" t="n">
+        <v>6</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795173</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136795176</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>375465</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6669999</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795176</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136795180</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>375480</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6670027</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795180</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136795188</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>375567</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6670017</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795188</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136795191</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>375545</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6669917</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795191</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>136830784</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>375623</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6670015</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136830784</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>136884187</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>375181</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6669756</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136884187</t>
         </is>
       </c>
     </row>
@@ -8443,6 +10096,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ82"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2689,45 +2689,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136765417</v>
+        <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79500</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
+          <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375284</v>
+        <v>375096</v>
       </c>
       <c r="R19" t="n">
-        <v>6669768</v>
+        <v>6669887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,22 +2757,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2778,6 +2771,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2795,13 +2789,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136765417</t>
+          <t>https://artportalen.se/Sighting/136886290</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136765632</v>
+        <v>136765417</v>
       </c>
       <c r="B20" t="n">
         <v>79500</v>
@@ -2836,13 +2830,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375291</v>
+        <v>375284</v>
       </c>
       <c r="R20" t="n">
-        <v>6669744</v>
+        <v>6669768</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2871,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2881,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2907,13 +2901,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136765632</t>
+          <t>https://artportalen.se/Sighting/136765417</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136765741</v>
+        <v>136765632</v>
       </c>
       <c r="B21" t="n">
         <v>79500</v>
@@ -2941,21 +2935,17 @@
           <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375262</v>
+        <v>375291</v>
       </c>
       <c r="R21" t="n">
-        <v>6669762</v>
+        <v>6669744</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2987,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,13 +3013,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136765741</t>
+          <t>https://artportalen.se/Sighting/136765632</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136884148</v>
+        <v>136765741</v>
       </c>
       <c r="B22" t="n">
         <v>79500</v>
@@ -3057,23 +3047,24 @@
           <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375242</v>
+        <v>375262</v>
       </c>
       <c r="R22" t="n">
-        <v>6669734</v>
+        <v>6669762</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3100,18 +3091,27 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3129,51 +3129,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884148</t>
+          <t>https://artportalen.se/Sighting/136765741</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136767140</v>
+        <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79233</v>
+        <v>79500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backarna, Backarna, Vrm</t>
+          <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375184</v>
+        <v>375242</v>
       </c>
       <c r="R23" t="n">
-        <v>6669750</v>
+        <v>6669734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3203,27 +3206,18 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3241,13 +3235,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767140</t>
+          <t>https://artportalen.se/Sighting/136884148</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136795167</v>
+        <v>136767140</v>
       </c>
       <c r="B24" t="n">
         <v>79233</v>
@@ -3278,17 +3272,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Backarna, Backarna, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375137</v>
+        <v>375184</v>
       </c>
       <c r="R24" t="n">
-        <v>6670153</v>
+        <v>6669750</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3312,22 +3306,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,24 +3336,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795167</t>
+          <t>https://artportalen.se/Sighting/136767140</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136795174</v>
+        <v>136795167</v>
       </c>
       <c r="B25" t="n">
         <v>79233</v>
@@ -3394,13 +3388,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375372</v>
+        <v>375137</v>
       </c>
       <c r="R25" t="n">
-        <v>6669927</v>
+        <v>6670153</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3429,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3439,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,13 +3459,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795174</t>
+          <t>https://artportalen.se/Sighting/136795167</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136795175</v>
+        <v>136795174</v>
       </c>
       <c r="B26" t="n">
         <v>79233</v>
@@ -3506,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375465</v>
+        <v>375372</v>
       </c>
       <c r="R26" t="n">
-        <v>6669999</v>
+        <v>6669927</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3541,7 +3535,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3551,7 +3545,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3577,13 +3571,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795175</t>
+          <t>https://artportalen.se/Sighting/136795174</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136795181</v>
+        <v>136795175</v>
       </c>
       <c r="B27" t="n">
         <v>79233</v>
@@ -3618,13 +3612,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375504</v>
+        <v>375465</v>
       </c>
       <c r="R27" t="n">
-        <v>6670028</v>
+        <v>6669999</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3653,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3663,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3689,13 +3683,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795181</t>
+          <t>https://artportalen.se/Sighting/136795175</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136795184</v>
+        <v>136795181</v>
       </c>
       <c r="B28" t="n">
         <v>79233</v>
@@ -3730,13 +3724,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375507</v>
+        <v>375504</v>
       </c>
       <c r="R28" t="n">
-        <v>6670034</v>
+        <v>6670028</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3765,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3775,7 +3769,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3801,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795184</t>
+          <t>https://artportalen.se/Sighting/136795181</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136821365</v>
+        <v>136795184</v>
       </c>
       <c r="B29" t="n">
         <v>79233</v>
@@ -3842,13 +3836,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375581</v>
+        <v>375507</v>
       </c>
       <c r="R29" t="n">
-        <v>6669867</v>
+        <v>6670034</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3872,22 +3866,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,13 +3907,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821365</t>
+          <t>https://artportalen.se/Sighting/136795184</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136821367</v>
+        <v>136821365</v>
       </c>
       <c r="B30" t="n">
         <v>79233</v>
@@ -3954,10 +3948,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375565</v>
+        <v>375581</v>
       </c>
       <c r="R30" t="n">
-        <v>6669859</v>
+        <v>6669867</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -3989,7 +3983,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3999,7 +3993,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4025,13 +4019,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821367</t>
+          <t>https://artportalen.se/Sighting/136821365</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136830783</v>
+        <v>136821367</v>
       </c>
       <c r="B31" t="n">
         <v>79233</v>
@@ -4066,13 +4060,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375726</v>
+        <v>375565</v>
       </c>
       <c r="R31" t="n">
-        <v>6670027</v>
+        <v>6669859</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4101,7 +4095,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4111,7 +4105,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4126,24 +4120,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830783</t>
+          <t>https://artportalen.se/Sighting/136821367</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136830785</v>
+        <v>136830783</v>
       </c>
       <c r="B32" t="n">
         <v>79233</v>
@@ -4178,13 +4172,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375623</v>
+        <v>375726</v>
       </c>
       <c r="R32" t="n">
-        <v>6670015</v>
+        <v>6670027</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4213,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4223,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4249,59 +4243,54 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830785</t>
+          <t>https://artportalen.se/Sighting/136830783</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136765556</v>
+        <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>58005</v>
+        <v>79233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
+          <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>375281</v>
+        <v>375623</v>
       </c>
       <c r="R33" t="n">
-        <v>6669749</v>
+        <v>6670015</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4325,22 +4314,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4366,13 +4355,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136765556</t>
+          <t>https://artportalen.se/Sighting/136830785</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136795190</v>
+        <v>136765556</v>
       </c>
       <c r="B34" t="n">
         <v>58005</v>
@@ -4408,17 +4397,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gäddtjärnen, Vrm</t>
+          <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>375547</v>
+        <v>375281</v>
       </c>
       <c r="R34" t="n">
-        <v>6669921</v>
+        <v>6669749</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4442,22 +4431,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,24 +4461,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795190</t>
+          <t>https://artportalen.se/Sighting/136765556</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136830758</v>
+        <v>136795190</v>
       </c>
       <c r="B35" t="n">
         <v>58005</v>
@@ -4518,19 +4507,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>375693</v>
+        <v>375547</v>
       </c>
       <c r="R35" t="n">
-        <v>6670228</v>
+        <v>6669921</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4554,27 +4548,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4589,24 +4578,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830758</t>
+          <t>https://artportalen.se/Sighting/136795190</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136830775</v>
+        <v>136830758</v>
       </c>
       <c r="B36" t="n">
         <v>58005</v>
@@ -4641,13 +4630,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>375853</v>
+        <v>375693</v>
       </c>
       <c r="R36" t="n">
-        <v>6670087</v>
+        <v>6670228</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4676,7 +4665,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4675,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4717,13 +4706,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830775</t>
+          <t>https://artportalen.se/Sighting/136830758</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136830787</v>
+        <v>136830775</v>
       </c>
       <c r="B37" t="n">
         <v>58005</v>
@@ -4758,10 +4747,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>375562</v>
+        <v>375853</v>
       </c>
       <c r="R37" t="n">
-        <v>6670005</v>
+        <v>6670087</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4793,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4803,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4834,13 +4823,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830787</t>
+          <t>https://artportalen.se/Sighting/136830775</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136830789</v>
+        <v>136830787</v>
       </c>
       <c r="B38" t="n">
         <v>58005</v>
@@ -4875,13 +4864,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>375449</v>
+        <v>375562</v>
       </c>
       <c r="R38" t="n">
-        <v>6669946</v>
+        <v>6670005</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4910,7 +4899,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4920,7 +4909,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4951,13 +4940,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830789</t>
+          <t>https://artportalen.se/Sighting/136830787</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136884549</v>
+        <v>136830789</v>
       </c>
       <c r="B39" t="n">
         <v>58005</v>
@@ -4986,27 +4975,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>375035</v>
+        <v>375449</v>
       </c>
       <c r="R39" t="n">
-        <v>6670063</v>
+        <v>6669946</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5030,12 +5011,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5061,13 +5057,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884549</t>
+          <t>https://artportalen.se/Sighting/136830789</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136884555</v>
+        <v>136884549</v>
       </c>
       <c r="B40" t="n">
         <v>58005</v>
@@ -5100,7 +5096,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5110,10 +5106,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>375050</v>
+        <v>375035</v>
       </c>
       <c r="R40" t="n">
-        <v>6670085</v>
+        <v>6670063</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5171,13 +5167,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884555</t>
+          <t>https://artportalen.se/Sighting/136884549</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136884705</v>
+        <v>136884555</v>
       </c>
       <c r="B41" t="n">
         <v>58005</v>
@@ -5210,7 +5206,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5220,10 +5216,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>375291</v>
+        <v>375050</v>
       </c>
       <c r="R41" t="n">
-        <v>6670056</v>
+        <v>6670085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5275,22 +5271,22 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Granback, Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884705</t>
+          <t>https://artportalen.se/Sighting/136884555</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136821364</v>
+        <v>136884705</v>
       </c>
       <c r="B42" t="n">
-        <v>57195</v>
+        <v>58005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5298,46 +5294,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>375694</v>
+        <v>375291</v>
       </c>
       <c r="R42" t="n">
-        <v>6669902</v>
+        <v>6670056</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5361,27 +5356,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Tupp stöttes</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5396,27 +5376,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821364</t>
+          <t>https://artportalen.se/Sighting/136884705</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136830766</v>
+        <v>136886185</v>
       </c>
       <c r="B43" t="n">
-        <v>57195</v>
+        <v>58005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,27 +5404,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5452,10 +5436,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>375884</v>
+        <v>375200</v>
       </c>
       <c r="R43" t="n">
-        <v>6670111</v>
+        <v>6669916</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5482,27 +5466,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,16 +5497,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830766</t>
+          <t>https://artportalen.se/Sighting/136886185</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136821347</v>
+        <v>136886411</v>
       </c>
       <c r="B44" t="n">
-        <v>57198</v>
+        <v>58005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5545,16 +5514,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5563,24 +5532,27 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>375327</v>
+        <v>375097</v>
       </c>
       <c r="R44" t="n">
-        <v>6669913</v>
+        <v>6669882</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5604,22 +5576,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Trumning o i flykt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5634,27 +5601,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821347</t>
+          <t>https://artportalen.se/Sighting/136886411</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136821357</v>
+        <v>136886461</v>
       </c>
       <c r="B45" t="n">
-        <v>58169</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5662,46 +5629,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>375890</v>
+        <v>375037</v>
       </c>
       <c r="R45" t="n">
-        <v>6670039</v>
+        <v>6669993</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5725,29 +5691,19 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5755,49 +5711,49 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821357</t>
+          <t>https://artportalen.se/Sighting/136886461</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136830786</v>
+        <v>136821364</v>
       </c>
       <c r="B46" t="n">
-        <v>58169</v>
+        <v>57195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5805,16 +5761,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>375599</v>
+        <v>375694</v>
       </c>
       <c r="R46" t="n">
-        <v>6670026</v>
+        <v>6669902</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5846,7 +5807,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5856,7 +5817,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tupp stöttes</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5871,56 +5837,52 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830786</t>
+          <t>https://artportalen.se/Sighting/136821364</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136884610</v>
+        <v>136830766</v>
       </c>
       <c r="B47" t="n">
-        <v>58169</v>
+        <v>57195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -5931,10 +5893,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>375138</v>
+        <v>375884</v>
       </c>
       <c r="R47" t="n">
-        <v>6670040</v>
+        <v>6670111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5961,12 +5923,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5986,22 +5963,22 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jesper Granback, Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884610</t>
+          <t>https://artportalen.se/Sighting/136830766</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136830748</v>
+        <v>136821347</v>
       </c>
       <c r="B48" t="n">
-        <v>58164</v>
+        <v>57198</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,16 +5986,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103023</v>
+        <v>102613</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6027,16 +6004,21 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>375478</v>
+        <v>375327</v>
       </c>
       <c r="R48" t="n">
-        <v>6670141</v>
+        <v>6669913</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6068,7 +6050,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6078,12 +6060,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flera</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6098,49 +6075,49 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830748</t>
+          <t>https://artportalen.se/Sighting/136821347</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136830772</v>
+        <v>136821357</v>
       </c>
       <c r="B49" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6148,19 +6125,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376001</v>
+        <v>375890</v>
       </c>
       <c r="R49" t="n">
-        <v>6670081</v>
+        <v>6670039</v>
       </c>
       <c r="S49" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6189,7 +6171,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6199,7 +6181,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6214,62 +6196,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830772</t>
+          <t>https://artportalen.se/Sighting/136821357</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136830778</v>
+        <v>136830786</v>
       </c>
       <c r="B50" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>375833</v>
+        <v>375599</v>
       </c>
       <c r="R50" t="n">
-        <v>6670068</v>
+        <v>6670026</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6301,7 +6287,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6311,7 +6297,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6337,38 +6323,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830778</t>
+          <t>https://artportalen.se/Sighting/136830786</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136884192</v>
+        <v>136884610</v>
       </c>
       <c r="B51" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6386,10 +6372,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>375171</v>
+        <v>375138</v>
       </c>
       <c r="R51" t="n">
-        <v>6669761</v>
+        <v>6670040</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6441,22 +6427,22 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884192</t>
+          <t>https://artportalen.se/Sighting/136884610</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136821370</v>
+        <v>136830748</v>
       </c>
       <c r="B52" t="n">
-        <v>58629</v>
+        <v>58164</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6464,43 +6450,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>375441</v>
+        <v>375478</v>
       </c>
       <c r="R52" t="n">
-        <v>6669799</v>
+        <v>6670141</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6532,7 +6509,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6542,7 +6519,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6557,27 +6539,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821370</t>
+          <t>https://artportalen.se/Sighting/136830748</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136830747</v>
+        <v>136830772</v>
       </c>
       <c r="B53" t="n">
-        <v>58629</v>
+        <v>58164</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6585,21 +6567,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6613,13 +6595,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>375482</v>
+        <v>376001</v>
       </c>
       <c r="R53" t="n">
-        <v>6670128</v>
+        <v>6670081</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6648,7 +6630,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6658,7 +6640,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6684,16 +6666,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830747</t>
+          <t>https://artportalen.se/Sighting/136830772</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136795169</v>
+        <v>136830778</v>
       </c>
       <c r="B54" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6701,39 +6683,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>375318</v>
+        <v>375833</v>
       </c>
       <c r="R54" t="n">
-        <v>6670152</v>
+        <v>6670068</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6760,22 +6737,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6786,46 +6763,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795169</t>
+          <t>https://artportalen.se/Sighting/136830778</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136795186</v>
+        <v>136884192</v>
       </c>
       <c r="B55" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,42 +6795,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>375569</v>
+        <v>375171</v>
       </c>
       <c r="R55" t="n">
-        <v>6670040</v>
+        <v>6669761</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6892,22 +6857,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6918,46 +6873,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795186</t>
+          <t>https://artportalen.se/Sighting/136884192</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136821351</v>
+        <v>136886243</v>
       </c>
       <c r="B56" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6965,42 +6905,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>375654</v>
+        <v>375163</v>
       </c>
       <c r="R56" t="n">
-        <v>6670285</v>
+        <v>6669972</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7024,22 +6967,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7054,27 +6987,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821351</t>
+          <t>https://artportalen.se/Sighting/136886243</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136830754</v>
+        <v>136821370</v>
       </c>
       <c r="B57" t="n">
-        <v>8463</v>
+        <v>58629</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7082,34 +7015,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>375623</v>
+        <v>375441</v>
       </c>
       <c r="R57" t="n">
-        <v>6670238</v>
+        <v>6669799</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7141,7 +7083,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7151,7 +7093,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7166,27 +7108,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830754</t>
+          <t>https://artportalen.se/Sighting/136821370</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136830755</v>
+        <v>136830747</v>
       </c>
       <c r="B58" t="n">
-        <v>8463</v>
+        <v>58629</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7194,34 +7136,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>375652</v>
+        <v>375482</v>
       </c>
       <c r="R58" t="n">
-        <v>6670242</v>
+        <v>6670128</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7253,7 +7199,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7263,12 +7209,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Mer färska spår</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7294,13 +7235,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830755</t>
+          <t>https://artportalen.se/Sighting/136830747</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136830756</v>
+        <v>136795169</v>
       </c>
       <c r="B59" t="n">
         <v>8463</v>
@@ -7329,16 +7270,21 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>375661</v>
+        <v>375318</v>
       </c>
       <c r="R59" t="n">
-        <v>6670269</v>
+        <v>6670152</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7365,22 +7311,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7391,28 +7337,43 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830756</t>
+          <t>https://artportalen.se/Sighting/136795169</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136830759</v>
+        <v>136795186</v>
       </c>
       <c r="B60" t="n">
         <v>8463</v>
@@ -7441,19 +7402,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>375693</v>
+        <v>375569</v>
       </c>
       <c r="R60" t="n">
-        <v>6670228</v>
+        <v>6670040</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7477,22 +7443,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7503,28 +7469,43 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830759</t>
+          <t>https://artportalen.se/Sighting/136795186</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136830760</v>
+        <v>136821351</v>
       </c>
       <c r="B61" t="n">
         <v>8463</v>
@@ -7553,16 +7534,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>375728</v>
+        <v>375654</v>
       </c>
       <c r="R61" t="n">
-        <v>6670132</v>
+        <v>6670285</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7594,7 +7580,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7604,7 +7590,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7619,24 +7605,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830760</t>
+          <t>https://artportalen.se/Sighting/136821351</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136830774</v>
+        <v>136830754</v>
       </c>
       <c r="B62" t="n">
         <v>8463</v>
@@ -7671,10 +7657,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>375850</v>
+        <v>375623</v>
       </c>
       <c r="R62" t="n">
-        <v>6670075</v>
+        <v>6670238</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7706,7 +7692,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7716,7 +7702,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7742,13 +7728,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830774</t>
+          <t>https://artportalen.se/Sighting/136830754</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136830776</v>
+        <v>136830755</v>
       </c>
       <c r="B63" t="n">
         <v>8463</v>
@@ -7783,10 +7769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>375853</v>
+        <v>375652</v>
       </c>
       <c r="R63" t="n">
-        <v>6670087</v>
+        <v>6670242</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7818,7 +7804,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7828,7 +7814,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Mer färska spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7854,13 +7845,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830776</t>
+          <t>https://artportalen.se/Sighting/136830755</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136830790</v>
+        <v>136830756</v>
       </c>
       <c r="B64" t="n">
         <v>8463</v>
@@ -7895,10 +7886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>375449</v>
+        <v>375661</v>
       </c>
       <c r="R64" t="n">
-        <v>6669946</v>
+        <v>6670269</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7930,7 +7921,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7940,7 +7931,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7966,13 +7957,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830790</t>
+          <t>https://artportalen.se/Sighting/136830756</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136830791</v>
+        <v>136830759</v>
       </c>
       <c r="B65" t="n">
         <v>8463</v>
@@ -8007,13 +7998,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>375461</v>
+        <v>375693</v>
       </c>
       <c r="R65" t="n">
-        <v>6669933</v>
+        <v>6670228</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8042,7 +8033,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8052,7 +8043,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8078,13 +8069,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830791</t>
+          <t>https://artportalen.se/Sighting/136830759</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136884662</v>
+        <v>136830760</v>
       </c>
       <c r="B66" t="n">
         <v>8463</v>
@@ -8113,24 +8104,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>375226</v>
+        <v>375728</v>
       </c>
       <c r="R66" t="n">
-        <v>6670098</v>
+        <v>6670132</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8154,12 +8140,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8168,7 +8164,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8180,19 +8175,19 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jesper Granback, Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884662</t>
+          <t>https://artportalen.se/Sighting/136830760</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136884706</v>
+        <v>136830774</v>
       </c>
       <c r="B67" t="n">
         <v>8463</v>
@@ -8221,24 +8216,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>375291</v>
+        <v>375850</v>
       </c>
       <c r="R67" t="n">
-        <v>6670056</v>
+        <v>6670075</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8262,12 +8252,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8276,7 +8276,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8288,68 +8287,60 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jesper Granback, Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136884706</t>
+          <t>https://artportalen.se/Sighting/136830774</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136830751</v>
+        <v>136830776</v>
       </c>
       <c r="B68" t="n">
-        <v>56739</v>
+        <v>8463</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>206046</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>hårrester</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>375557</v>
+        <v>375853</v>
       </c>
       <c r="R68" t="n">
-        <v>6670167</v>
+        <v>6670087</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8378,7 +8369,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8388,7 +8379,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8414,59 +8405,51 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830751</t>
+          <t>https://artportalen.se/Sighting/136830776</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136830761</v>
+        <v>136830790</v>
       </c>
       <c r="B69" t="n">
-        <v>56739</v>
+        <v>8463</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>206046</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>375752</v>
+        <v>375449</v>
       </c>
       <c r="R69" t="n">
-        <v>6670115</v>
+        <v>6669946</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8498,7 +8481,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8508,7 +8491,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8534,16 +8517,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830761</t>
+          <t>https://artportalen.se/Sighting/136830790</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136795185</v>
+        <v>136830791</v>
       </c>
       <c r="B70" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8551,38 +8534,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>375520</v>
+        <v>375461</v>
       </c>
       <c r="R70" t="n">
-        <v>6670059</v>
+        <v>6669933</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8609,22 +8588,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8639,27 +8618,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795185</t>
+          <t>https://artportalen.se/Sighting/136830791</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136821356</v>
+        <v>136884662</v>
       </c>
       <c r="B71" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8667,46 +8646,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>375908</v>
+        <v>375226</v>
       </c>
       <c r="R71" t="n">
-        <v>6670081</v>
+        <v>6670098</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8730,22 +8705,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8754,33 +8719,34 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821356</t>
+          <t>https://artportalen.se/Sighting/136884662</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136821360</v>
+        <v>136884706</v>
       </c>
       <c r="B72" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8788,46 +8754,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>375747</v>
+        <v>375291</v>
       </c>
       <c r="R72" t="n">
-        <v>6669937</v>
+        <v>6670056</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8851,22 +8813,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8875,33 +8827,34 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821360</t>
+          <t>https://artportalen.se/Sighting/136884706</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136821361</v>
+        <v>136886108</v>
       </c>
       <c r="B73" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8909,46 +8862,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>375768</v>
+        <v>375250</v>
       </c>
       <c r="R73" t="n">
-        <v>6669986</v>
+        <v>6669788</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8972,22 +8921,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8996,33 +8935,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136821361</t>
+          <t>https://artportalen.se/Sighting/136886108</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136830781</v>
+        <v>136886140</v>
       </c>
       <c r="B74" t="n">
-        <v>99270</v>
+        <v>8463</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9030,41 +8970,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>375712</v>
+        <v>375246</v>
       </c>
       <c r="R74" t="n">
-        <v>6670070</v>
+        <v>6669798</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9088,27 +9029,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Torra frökapslar</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9117,6 +9043,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9134,16 +9061,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830781</t>
+          <t>https://artportalen.se/Sighting/136886140</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136795170</v>
+        <v>136886155</v>
       </c>
       <c r="B75" t="n">
-        <v>98215</v>
+        <v>8463</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9151,37 +9078,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>375450</v>
+        <v>375241</v>
       </c>
       <c r="R75" t="n">
-        <v>6670180</v>
+        <v>6669821</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9208,92 +9140,88 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795170</t>
+          <t>https://artportalen.se/Sighting/136886155</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136795173</v>
+        <v>136886159</v>
       </c>
       <c r="B76" t="n">
-        <v>79234</v>
+        <v>8463</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>375476</v>
+        <v>375225</v>
       </c>
       <c r="R76" t="n">
-        <v>6670112</v>
+        <v>6669869</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9320,54 +9248,45 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795173</t>
+          <t>https://artportalen.se/Sighting/136886159</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136795176</v>
+        <v>136830751</v>
       </c>
       <c r="B77" t="n">
-        <v>79234</v>
+        <v>56739</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9375,37 +9294,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>206046</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>375465</v>
+        <v>375557</v>
       </c>
       <c r="R77" t="n">
-        <v>6669999</v>
+        <v>6670167</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9429,22 +9356,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9459,27 +9386,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795176</t>
+          <t>https://artportalen.se/Sighting/136830751</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136795180</v>
+        <v>136830761</v>
       </c>
       <c r="B78" t="n">
-        <v>79234</v>
+        <v>56739</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9487,34 +9414,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>206046</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>375480</v>
+        <v>375752</v>
       </c>
       <c r="R78" t="n">
-        <v>6670027</v>
+        <v>6670115</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9541,22 +9476,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9571,62 +9506,66 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795180</t>
+          <t>https://artportalen.se/Sighting/136830761</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136795188</v>
+        <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>79234</v>
+        <v>99270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>375567</v>
+        <v>375520</v>
       </c>
       <c r="R79" t="n">
-        <v>6670017</v>
+        <v>6670059</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9658,7 +9597,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9668,7 +9607,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9694,54 +9633,63 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795188</t>
+          <t>https://artportalen.se/Sighting/136795185</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136795191</v>
+        <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>79234</v>
+        <v>99270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>375545</v>
+        <v>375908</v>
       </c>
       <c r="R80" t="n">
-        <v>6669917</v>
+        <v>6670081</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9765,22 +9713,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9806,51 +9754,60 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795191</t>
+          <t>https://artportalen.se/Sighting/136821356</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136830784</v>
+        <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>79234</v>
+        <v>99270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>375623</v>
+        <v>375747</v>
       </c>
       <c r="R81" t="n">
-        <v>6670015</v>
+        <v>6669937</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9882,7 +9839,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9892,7 +9849,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9907,68 +9864,74 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136830784</t>
+          <t>https://artportalen.se/Sighting/136821360</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136884187</v>
+        <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>79234</v>
+        <v>99270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>375181</v>
+        <v>375768</v>
       </c>
       <c r="R82" t="n">
-        <v>6669756</v>
+        <v>6669986</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9992,12 +9955,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10006,23 +9979,1033 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821361</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136830781</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>375712</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6670070</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Torra frökapslar</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830781</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136795170</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>375450</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6670180</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795170</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136795173</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>375476</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6670112</v>
+      </c>
+      <c r="S85" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795173</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>136795176</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>375465</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6669999</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795176</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136795180</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>375480</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6670027</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795180</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>136795188</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>375567</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6670017</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795188</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>136795191</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>375545</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6669917</v>
+      </c>
+      <c r="S89" t="n">
+        <v>7</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795191</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>136830784</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>375623</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6670015</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830784</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>136884187</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Gäddtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>375181</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6669756</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136884187</t>
         </is>
@@ -10111,6 +11094,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97681</v>
+        <v>97687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97687</v>
+        <v>97689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97689</v>
+        <v>97690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97690</v>
+        <v>97696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97696</v>
+        <v>97700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97700</v>
+        <v>97702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jesper Granback, Jens Johansen</t>
+          <t>Jens Johansen, Jesper Granback</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>136765556</v>
       </c>
       <c r="B34" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>136795190</v>
       </c>
       <c r="B35" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>136830758</v>
       </c>
       <c r="B36" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>136830775</v>
       </c>
       <c r="B37" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136830787</v>
       </c>
       <c r="B38" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136830789</v>
       </c>
       <c r="B39" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136884549</v>
       </c>
       <c r="B40" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>136884555</v>
       </c>
       <c r="B41" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136884705</v>
       </c>
       <c r="B42" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>136886185</v>
       </c>
       <c r="B43" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136886411</v>
       </c>
       <c r="B44" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>136886461</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136821364</v>
       </c>
       <c r="B46" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136830766</v>
       </c>
       <c r="B47" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136821347</v>
       </c>
       <c r="B48" t="n">
-        <v>57198</v>
+        <v>57211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>136821357</v>
       </c>
       <c r="B49" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>136830786</v>
       </c>
       <c r="B50" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136884610</v>
       </c>
       <c r="B51" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>136830748</v>
       </c>
       <c r="B52" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>136830772</v>
       </c>
       <c r="B53" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136830778</v>
       </c>
       <c r="B54" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>136884192</v>
       </c>
       <c r="B55" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136886243</v>
       </c>
       <c r="B56" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136821370</v>
       </c>
       <c r="B57" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>136830747</v>
       </c>
       <c r="B58" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jens Johansen, Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9286,7 +9286,7 @@
         <v>136830751</v>
       </c>
       <c r="B77" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>136830761</v>
       </c>
       <c r="B78" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97717</v>
+        <v>97719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>136765556</v>
       </c>
       <c r="B34" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>136795190</v>
       </c>
       <c r="B35" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>136830758</v>
       </c>
       <c r="B36" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>136830775</v>
       </c>
       <c r="B37" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136830787</v>
       </c>
       <c r="B38" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136830789</v>
       </c>
       <c r="B39" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136884549</v>
       </c>
       <c r="B40" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>136884555</v>
       </c>
       <c r="B41" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136884705</v>
       </c>
       <c r="B42" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>136886185</v>
       </c>
       <c r="B43" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136886411</v>
       </c>
       <c r="B44" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>136886461</v>
       </c>
       <c r="B45" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136821364</v>
       </c>
       <c r="B46" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136830766</v>
       </c>
       <c r="B47" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136821347</v>
       </c>
       <c r="B48" t="n">
-        <v>57211</v>
+        <v>57213</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>136821357</v>
       </c>
       <c r="B49" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>136830786</v>
       </c>
       <c r="B50" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136884610</v>
       </c>
       <c r="B51" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>136830748</v>
       </c>
       <c r="B52" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>136830772</v>
       </c>
       <c r="B53" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136830778</v>
       </c>
       <c r="B54" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>136884192</v>
       </c>
       <c r="B55" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136886243</v>
       </c>
       <c r="B56" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136821370</v>
       </c>
       <c r="B57" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>136830747</v>
       </c>
       <c r="B58" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>136795169</v>
       </c>
       <c r="B59" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>136795186</v>
       </c>
       <c r="B60" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>136821351</v>
       </c>
       <c r="B61" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>136830754</v>
       </c>
       <c r="B62" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>136830755</v>
       </c>
       <c r="B63" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136830756</v>
       </c>
       <c r="B64" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>136830759</v>
       </c>
       <c r="B65" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>136830760</v>
       </c>
       <c r="B66" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>136830774</v>
       </c>
       <c r="B67" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>136830776</v>
       </c>
       <c r="B68" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>136830790</v>
       </c>
       <c r="B69" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>136830791</v>
       </c>
       <c r="B70" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136884662</v>
       </c>
       <c r="B71" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>136884706</v>
       </c>
       <c r="B72" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136886108</v>
       </c>
       <c r="B73" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>136886140</v>
       </c>
       <c r="B74" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>136886155</v>
       </c>
       <c r="B75" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>136886159</v>
       </c>
       <c r="B76" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>136830751</v>
       </c>
       <c r="B77" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>136830761</v>
       </c>
       <c r="B78" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -4390,11 +4390,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västra Gäddflyet, Västra Gäddflyet, Vrm</t>
@@ -4507,11 +4503,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -5094,11 +5086,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5204,11 +5192,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5314,11 +5298,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5424,11 +5404,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5534,11 +5510,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5649,11 +5621,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5761,11 +5729,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -6004,11 +5968,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -6125,11 +6085,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -7037,11 +6993,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -7270,11 +7222,7 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -7402,11 +7350,7 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -7534,11 +7478,7 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gäddtjärnen, Vrm</t>
@@ -9314,11 +9254,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>hårrester</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9434,11 +9370,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97719</v>
+        <v>97722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97722</v>
+        <v>97732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>136765556</v>
       </c>
       <c r="B34" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>136795190</v>
       </c>
       <c r="B35" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>136830758</v>
       </c>
       <c r="B36" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>136830775</v>
       </c>
       <c r="B37" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>136830787</v>
       </c>
       <c r="B38" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>136830789</v>
       </c>
       <c r="B39" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>136884549</v>
       </c>
       <c r="B40" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>136884555</v>
       </c>
       <c r="B41" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136884705</v>
       </c>
       <c r="B42" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>136886185</v>
       </c>
       <c r="B43" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>136886411</v>
       </c>
       <c r="B44" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136886461</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>136821364</v>
       </c>
       <c r="B46" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136830766</v>
       </c>
       <c r="B47" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>136821347</v>
       </c>
       <c r="B48" t="n">
-        <v>57213</v>
+        <v>57223</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136821357</v>
       </c>
       <c r="B49" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>136830786</v>
       </c>
       <c r="B50" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136884610</v>
       </c>
       <c r="B51" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>136830748</v>
       </c>
       <c r="B52" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>136830772</v>
       </c>
       <c r="B53" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>136830778</v>
       </c>
       <c r="B54" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>136884192</v>
       </c>
       <c r="B55" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136886243</v>
       </c>
       <c r="B56" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136821370</v>
       </c>
       <c r="B57" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>136830747</v>
       </c>
       <c r="B58" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136795169</v>
       </c>
       <c r="B59" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>136795186</v>
       </c>
       <c r="B60" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>136821351</v>
       </c>
       <c r="B61" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>136830754</v>
       </c>
       <c r="B62" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>136830755</v>
       </c>
       <c r="B63" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>136830756</v>
       </c>
       <c r="B64" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>136830759</v>
       </c>
       <c r="B65" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>136830760</v>
       </c>
       <c r="B66" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136830774</v>
       </c>
       <c r="B67" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136830776</v>
       </c>
       <c r="B68" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>136830790</v>
       </c>
       <c r="B69" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136830791</v>
       </c>
       <c r="B70" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>136884662</v>
       </c>
       <c r="B71" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>136884706</v>
       </c>
       <c r="B72" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136886108</v>
       </c>
       <c r="B73" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>136886140</v>
       </c>
       <c r="B74" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>136886155</v>
       </c>
       <c r="B75" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>136886159</v>
       </c>
       <c r="B76" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136830751</v>
       </c>
       <c r="B77" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136830761</v>
       </c>
       <c r="B78" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97732</v>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97733</v>
+        <v>97738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>136765556</v>
       </c>
       <c r="B34" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>136795190</v>
       </c>
       <c r="B35" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>136830758</v>
       </c>
       <c r="B36" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>136830775</v>
       </c>
       <c r="B37" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>136830787</v>
       </c>
       <c r="B38" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>136830789</v>
       </c>
       <c r="B39" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>136884549</v>
       </c>
       <c r="B40" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>136884555</v>
       </c>
       <c r="B41" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136884705</v>
       </c>
       <c r="B42" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>136886185</v>
       </c>
       <c r="B43" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>136886411</v>
       </c>
       <c r="B44" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136886461</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>136821364</v>
       </c>
       <c r="B46" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136830766</v>
       </c>
       <c r="B47" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>136821347</v>
       </c>
       <c r="B48" t="n">
-        <v>57223</v>
+        <v>57224</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136821357</v>
       </c>
       <c r="B49" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>136830786</v>
       </c>
       <c r="B50" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136884610</v>
       </c>
       <c r="B51" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>136830748</v>
       </c>
       <c r="B52" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>136830772</v>
       </c>
       <c r="B53" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>136830778</v>
       </c>
       <c r="B54" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>136884192</v>
       </c>
       <c r="B55" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136886243</v>
       </c>
       <c r="B56" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136821370</v>
       </c>
       <c r="B57" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>136830747</v>
       </c>
       <c r="B58" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>136830751</v>
       </c>
       <c r="B77" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136830761</v>
       </c>
       <c r="B78" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97738</v>
+        <v>97740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97740</v>
+        <v>97746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>136795189</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>136795168</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>136821353</v>
       </c>
       <c r="B5" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136795179</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136821355</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136821362</v>
       </c>
       <c r="B12" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136795165</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>136821366</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136821369</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>136795167</v>
       </c>
       <c r="B25" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>136795174</v>
       </c>
       <c r="B26" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136795175</v>
       </c>
       <c r="B27" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136795181</v>
       </c>
       <c r="B28" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136795184</v>
       </c>
       <c r="B29" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136821365</v>
       </c>
       <c r="B30" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>136821367</v>
       </c>
       <c r="B31" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>136765556</v>
       </c>
       <c r="B34" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>136795190</v>
       </c>
       <c r="B35" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>136830758</v>
       </c>
       <c r="B36" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>136830775</v>
       </c>
       <c r="B37" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>136830787</v>
       </c>
       <c r="B38" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>136830789</v>
       </c>
       <c r="B39" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>136884549</v>
       </c>
       <c r="B40" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>136884555</v>
       </c>
       <c r="B41" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136884705</v>
       </c>
       <c r="B42" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>136886185</v>
       </c>
       <c r="B43" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>136886411</v>
       </c>
       <c r="B44" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136886461</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136821357</v>
       </c>
       <c r="B49" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>136830786</v>
       </c>
       <c r="B50" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136884610</v>
       </c>
       <c r="B51" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>136830748</v>
       </c>
       <c r="B52" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>136830772</v>
       </c>
       <c r="B53" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>136830778</v>
       </c>
       <c r="B54" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>136884192</v>
       </c>
       <c r="B55" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136886243</v>
       </c>
       <c r="B56" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136821370</v>
       </c>
       <c r="B57" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>136830747</v>
       </c>
       <c r="B58" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>136795185</v>
       </c>
       <c r="B79" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>136821356</v>
       </c>
       <c r="B80" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>136821360</v>
       </c>
       <c r="B81" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136821361</v>
       </c>
       <c r="B82" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136795170</v>
       </c>
       <c r="B84" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>136795173</v>
       </c>
       <c r="B85" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>136795176</v>
       </c>
       <c r="B86" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>136795180</v>
       </c>
       <c r="B87" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>136795188</v>
       </c>
       <c r="B88" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>136795191</v>
       </c>
       <c r="B89" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830764</v>
       </c>
       <c r="B2" t="n">
-        <v>97746</v>
+        <v>97758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136830765</v>
       </c>
       <c r="B6" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136830762</v>
       </c>
       <c r="B8" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136830780</v>
       </c>
       <c r="B9" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136847994</v>
       </c>
       <c r="B13" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136830752</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>136830767</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>136830783</v>
       </c>
       <c r="B32" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>136830785</v>
       </c>
       <c r="B33" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>136830781</v>
       </c>
       <c r="B83" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>136830784</v>
       </c>
       <c r="B90" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136884160</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136765417</v>
       </c>
       <c r="B20" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136765632</v>
       </c>
       <c r="B21" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136765741</v>
       </c>
       <c r="B22" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>136884148</v>
       </c>
       <c r="B23" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136767140</v>
       </c>
       <c r="B24" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>136884187</v>
       </c>
       <c r="B91" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34924-2026 artfynd.xlsx
+++ b/artfynd/A 34924-2026 artfynd.xlsx
@@ -2692,7 +2692,7 @@
         <v>136886290</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
